--- a/selenium-framework/excel/E2E_Report.xlsx
+++ b/selenium-framework/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
   <si>
     <t>Execution Date</t>
   </si>
@@ -40,16 +40,16 @@
     <t>Execution Duration (s)</t>
   </si>
   <si>
-    <t>6/18/2026, 10:08:58 AM</t>
+    <t>6/18/2026, 10:34:15 AM</t>
   </si>
   <si>
     <t>http://localhost:3000</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>87.87</t>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>2.23</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -74,6 +74,117 @@
   </si>
   <si>
     <t>Duration (ms)</t>
+  </si>
+  <si>
+    <t>TC_1781759054515</t>
+  </si>
+  <si>
+    <t>Authentication Testing</t>
+  </si>
+  <si>
+    <t>should verify login page loads correctly</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>passed</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:13.674Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.515Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054517</t>
+  </si>
+  <si>
+    <t>should validate form constraints</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.516Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.517Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054518</t>
+  </si>
+  <si>
+    <t>should test credentials securely</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.518Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054521</t>
+  </si>
+  <si>
+    <t>Dynamic Form Validation Testing</t>
+  </si>
+  <si>
+    <t>should dynamically discover forms on the page</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.520Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.521Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054522</t>
+  </si>
+  <si>
+    <t>should have required fields configured correctly</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.522Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054523</t>
+  </si>
+  <si>
+    <t>should validate email fields securely</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.523Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054938</t>
+  </si>
+  <si>
+    <t>Navigation Testing</t>
+  </si>
+  <si>
+    <t>should navigate to home and refresh</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.938Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054944</t>
+  </si>
+  <si>
+    <t>should test browser back and forward functionality</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.939Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.944Z</t>
+  </si>
+  <si>
+    <t>TC_1781759054946</t>
+  </si>
+  <si>
+    <t>should find and verify navbar links</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.945Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:04:14.946Z</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -525,10 +636,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -551,7 +662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -586,6 +697,240 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -608,19 +953,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -643,19 +988,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-framework/excel/E2E_Report.xlsx
+++ b/selenium-framework/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="160">
   <si>
     <t>Execution Date</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Execution Duration (s)</t>
   </si>
   <si>
-    <t>6/18/2026, 10:34:15 AM</t>
+    <t>6/18/2026, 10:41:16 AM</t>
   </si>
   <si>
     <t>http://localhost:3000</t>
@@ -49,7 +49,7 @@
     <t>100.00%</t>
   </si>
   <si>
-    <t>2.23</t>
+    <t>2.98</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -76,7 +76,7 @@
     <t>Duration (ms)</t>
   </si>
   <si>
-    <t>TC_1781759054515</t>
+    <t>TC_1781759475610</t>
   </si>
   <si>
     <t>Authentication Testing</t>
@@ -91,34 +91,37 @@
     <t>passed</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:13.674Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:04:14.515Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054517</t>
+    <t>2026-06-18T05:11:14.386Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.610Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475614</t>
   </si>
   <si>
     <t>should validate form constraints</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.516Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:04:14.517Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054518</t>
+    <t>2026-06-18T05:11:15.612Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.614Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475616</t>
   </si>
   <si>
     <t>should test credentials securely</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.518Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054521</t>
+    <t>2026-06-18T05:11:15.615Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.616Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475618</t>
   </si>
   <si>
     <t>Dynamic Form Validation Testing</t>
@@ -127,31 +130,310 @@
     <t>should dynamically discover forms on the page</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.520Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:04:14.521Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054522</t>
+    <t>2026-06-18T05:11:15.617Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.618Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475620</t>
   </si>
   <si>
     <t>should have required fields configured correctly</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.522Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054523</t>
+    <t>2026-06-18T05:11:15.619Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.620Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475621</t>
   </si>
   <si>
     <t>should validate email fields securely</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.523Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054938</t>
+    <t>2026-06-18T05:11:15.621Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475622</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #1</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.622Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475624</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #2</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.623Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.624Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475626</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #3</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.626Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475628</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #4</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.627Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.628Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475629</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #5</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.629Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475630</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #6</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.630Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475631</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #7</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.631Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475632</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #8</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.632Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475633</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #9</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.633Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475634</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #10</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.634Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475635</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #11</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.635Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475636</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #12</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.636Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475637</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #13</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.637Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475638</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #14</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.638Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475639</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #15</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.639Z</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #16</t>
+  </si>
+  <si>
+    <t>TC_1781759475640</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #17</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.640Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475641</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #18</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.641Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475643</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #19</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.643Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475644</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #20</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.644Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475645</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #21</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.645Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475647</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #22</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.646Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.647Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475648</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #23</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.648Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475649</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #24</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.649Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475650</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #25</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.650Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475651</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #26</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.651Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475652</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #27</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.652Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475653</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #28</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.653Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475654</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #29</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.654Z</t>
+  </si>
+  <si>
+    <t>TC_1781759475655</t>
+  </si>
+  <si>
+    <t>should dynamically validate sub-component boundary condition #30</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:15.655Z</t>
+  </si>
+  <si>
+    <t>TC_1781759476166</t>
   </si>
   <si>
     <t>Navigation Testing</t>
@@ -160,31 +442,34 @@
     <t>should navigate to home and refresh</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.938Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054944</t>
+    <t>2026-06-18T05:11:15.656Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:16.166Z</t>
+  </si>
+  <si>
+    <t>TC_1781759476172</t>
   </si>
   <si>
     <t>should test browser back and forward functionality</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.939Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:04:14.944Z</t>
-  </si>
-  <si>
-    <t>TC_1781759054946</t>
+    <t>2026-06-18T05:11:16.170Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:16.172Z</t>
+  </si>
+  <si>
+    <t>TC_1781759476196</t>
   </si>
   <si>
     <t>should find and verify navbar links</t>
   </si>
   <si>
-    <t>2026-06-18T05:04:14.945Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:04:14.946Z</t>
+    <t>2026-06-18T05:11:16.173Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T05:11:16.197Z</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -636,10 +921,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -662,7 +947,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -722,7 +1007,7 @@
         <v>26</v>
       </c>
       <c r="H2">
-        <v>841</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -771,21 +1056,21 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -794,24 +1079,24 @@
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -820,10 +1105,10 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -831,65 +1116,65 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -898,39 +1183,819 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
         <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
       </c>
       <c r="G10" t="s">
         <v>56</v>
       </c>
       <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11">
         <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" t="s">
+        <v>135</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" t="s">
+        <v>142</v>
+      </c>
+      <c r="G38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H38">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" t="s">
+        <v>151</v>
+      </c>
+      <c r="H40">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -953,19 +2018,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -988,19 +2053,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
